--- a/test-cases/TestCases_1.0.xlsx
+++ b/test-cases/TestCases_1.0.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\WORK\LEARNING\QA Engineer\Internship\1t-cypress-e2e-telnyx\test-cases\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF793744-B08F-4EBC-B1A9-9073D9D7DF75}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB06A01B-BDD3-4BCA-B05E-4AE01FDF30E9}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15990" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/test-cases/TestCases_1.0.xlsx
+++ b/test-cases/TestCases_1.0.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\WORK\LEARNING\QA Engineer\Internship\1t-cypress-e2e-telnyx\test-cases\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB06A01B-BDD3-4BCA-B05E-4AE01FDF30E9}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E33BA9D-85DF-462B-A8F9-EBC925BE6385}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15990" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
